--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260826_223458.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260826_223458.xlsx
@@ -7154,7 +7154,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7376,7 +7376,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7598,7 +7598,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260826_223458.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260826_223458.xlsx
@@ -7154,7 +7154,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7376,7 +7376,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7598,7 +7598,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
